--- a/pipefy-crm/dados/relatorio_completo.xlsx
+++ b/pipefy-crm/dados/relatorio_completo.xlsx
@@ -465,7 +465,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>874</v>
+        <v>910</v>
       </c>
       <c r="D2" t="n">
         <v>108</v>
@@ -474,7 +474,7 @@
         <v>68</v>
       </c>
       <c r="F2" t="n">
-        <v>1051</v>
+        <v>1087</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -487,22 +487,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
         <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G3" t="n">
-        <v>46.4</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="4">
@@ -512,22 +512,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -540,13 +540,13 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>35</v>
@@ -562,22 +562,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>10.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="7">
@@ -590,13 +590,13 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>18</v>
@@ -621,13 +621,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="9">
@@ -665,7 +665,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -674,10 +674,10 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -741,94 +741,94 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D2" t="n">
         <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="G2" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Joana Rei Barreto da Costa</t>
+          <t>Ana Clara Belmonte Garcia</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Estela Vianna</t>
+          <t>Joana Rei Barreto da Costa</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ana Clara Belmonte Garcia</t>
+          <t>Estela Vianna</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6">
@@ -859,51 +859,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jonas Pimenta</t>
+          <t>Miguel Mendes Louzada de Souza</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G7" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Miguel Mendes Louzada de Souza</t>
+          <t>Jonas Pimenta</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
         <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="9">
@@ -959,126 +959,126 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gabriela Boechat</t>
+          <t>Manuella Heringer Rocha Verbicaro Ramos</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
         <v>90</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rodrigo Polly Anthés</t>
+          <t>Gabriela Boechat</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G12" t="n">
-        <v>13.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manuella Heringer Rocha Verbicaro Ramos</t>
+          <t>Rodrigo Polly Anthés</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marcos Paulo Santos</t>
+          <t>Camilla Ribeiro Ferreira</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>51</v>
+      </c>
+      <c r="D14" t="n">
         <v>6</v>
       </c>
-      <c r="C14" t="n">
-        <v>65</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F14" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G14" t="n">
-        <v>8.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Camilla Ribeiro Ferreira</t>
+          <t>Marcos Paulo Santos</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="16">
@@ -1109,51 +1109,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lucas Pimenta</t>
+          <t>Gabriel Saldanha</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>64</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gabriel Saldanha</t>
+          <t>Lucas Pimenta</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>12.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
         <v>33</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -1178,7 +1178,7 @@
         <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>11.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="20">
@@ -1191,13 +1191,13 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>56</v>
@@ -1216,10 +1216,10 @@
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -1234,51 +1234,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Beatriz Assunção</t>
+          <t>Guilherme Vanni de Lima Cavalcanti Wanderley</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
-        <v>8.300000000000001</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Guilherme Vanni de Lima Cavalcanti Wanderley</t>
+          <t>Beatriz Assunção</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
         <v>11</v>
@@ -1372,13 +1372,13 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
         <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>4.3</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1534,17 +1534,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paulo Vitor Couto</t>
+          <t>Pedro de Souza Angelo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
@@ -1553,98 +1553,98 @@
         <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>9.1</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Heitor Mendes</t>
+          <t>Paulo Vitor Couto</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enzo Antunes Marmello</t>
+          <t>Heitor Mendes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G36" t="n">
-        <v>44.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pedro de Souza Angelo</t>
+          <t>Enzo Antunes Marmello</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
         <v>3</v>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>marcos.paulo</t>
+          <t>Gilson Batista Machado Martins</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1653,23 +1653,23 @@
         <v>7</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gilson Batista Machado Martins</t>
+          <t>marcos.paulo</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>7</v>
       </c>
       <c r="G39" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1734,42 +1734,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sem responsável</t>
+          <t>Renato Saboia</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Renato Saboia</t>
+          <t>Eduarda Braun Monteiro da Silva</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -1778,26 +1778,26 @@
         <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Eduarda Braun Monteiro da Silva</t>
+          <t>Sem responsável</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
         <v>3</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -1809,17 +1809,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cecília Nogueira Rosa</t>
+          <t>João Victor Moraes</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -1834,17 +1834,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Vitor Malfa</t>
+          <t>Cecília Nogueira Rosa</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1859,7 +1859,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>João Victor Moraes</t>
+          <t>Vitor Malfa</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
@@ -1934,45 +1934,45 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Clara Guedes Fernandes</t>
+          <t>Eduardo Caldas</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mariana Fonseca</t>
+          <t>Clara Guedes Fernandes</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>2</v>
@@ -1984,11 +1984,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Eduardo Caldas</t>
+          <t>brunacatalani1-20261</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1997,26 +1997,26 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
         <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Arthur Catelani Gomes da Silva</t>
+          <t>Mariana Fonseca</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2025,26 +2025,26 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Heitor Ferreira</t>
+          <t>Arthur Catelani Gomes da Silva</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2053,23 +2053,23 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Guilherme Lameck</t>
+          <t>Heitor Ferreira</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nicollas Viellas Lee</t>
+          <t>Guilherme Lameck</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2103,23 +2103,23 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LUCAS CORDEIRO QUIRINO</t>
+          <t>Nicollas Viellas Lee</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -2128,23 +2128,23 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rafael Gondim</t>
+          <t>LUCAS CORDEIRO QUIRINO</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2153,20 +2153,20 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ericheubel-20241</t>
+          <t>Rafael Gondim</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2178,13 +2178,13 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>leonardorussosalles</t>
+          <t>ericheubel-20241</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2209,25 +2209,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>leonardorussosalles</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>liviamonteiro-poli</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2242,7 +2267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2259,7 +2284,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2267,12 +2292,12 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>985</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2285,7 +2310,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2293,7 +2318,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -2306,29 +2331,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3. Pré-diagnóstico feito</t>
+          <t>7. Follow-up</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. Oportunidade</t>
+          <t>3. Pré-diagnóstico feito</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2337,20 +2362,20 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7. Follow-up</t>
+          <t>1. Oportunidade</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2358,12 +2383,12 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2371,20 +2396,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4. Diagnóstico feito</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/pipefy-crm/dados/relatorio_completo.xlsx
+++ b/pipefy-crm/dados/relatorio_completo.xlsx
@@ -465,16 +465,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="D2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
-        <v>1087</v>
+        <v>1109</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -490,7 +490,7 @@
         <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
         <v>18</v>
@@ -499,10 +499,10 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G3" t="n">
-        <v>46.8</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="4">
@@ -568,10 +568,10 @@
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
@@ -671,13 +671,13 @@
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +741,7 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D2" t="n">
         <v>23</v>
@@ -750,7 +750,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G2" t="n">
         <v>7.7</v>
@@ -766,19 +766,19 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -869,16 +869,16 @@
         <v>91</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="8">
@@ -891,19 +891,19 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G8" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -941,13 +941,13 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>97</v>
@@ -966,16 +966,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G11" t="n">
         <v>2.2</v>
@@ -1041,19 +1041,19 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -1366,19 +1366,19 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1459,42 +1459,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gabriela D’Agostini Fraga</t>
+          <t>Gabriel Pereira</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
         <v>15</v>
       </c>
       <c r="G31" t="n">
-        <v>6.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Davison Dhiego de Farias Mazzei</t>
+          <t>Gabriela D’Agostini Fraga</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1503,32 +1503,32 @@
         <v>15</v>
       </c>
       <c r="G32" t="n">
-        <v>13.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gabriel Pereira</t>
+          <t>Davison Dhiego de Farias Mazzei</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G33" t="n">
-        <v>35.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="34">
@@ -1684,26 +1684,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>wallisonpereira-20221-poli</t>
+          <t>Sem responsável</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1734,114 +1734,114 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Renato Saboia</t>
+          <t>João Victor Moraes</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Eduarda Braun Monteiro da Silva</t>
+          <t>wallisonpereira-20221-poli</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sem responsável</t>
+          <t>Renato Saboia</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>João Victor Moraes</t>
+          <t>Clara Guedes Fernandes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cecília Nogueira Rosa</t>
+          <t>Eduarda Braun Monteiro da Silva</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -1850,48 +1850,48 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Vitor Malfa</t>
+          <t>brunacatalani1-20261</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stella Monteiro</t>
+          <t>Cecília Nogueira Rosa</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -1903,13 +1903,13 @@
         <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lucas Angelo Ribeiro</t>
+          <t>Vitor Malfa</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1922,82 +1922,82 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Eduardo Caldas</t>
+          <t>Stella Monteiro</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Clara Guedes Fernandes</t>
+          <t>Lucas Angelo Ribeiro</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>brunacatalani1-20261</t>
+          <t>Mariana Fonseca</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>2</v>
@@ -2009,14 +2009,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mariana Fonseca</t>
+          <t>Eduardo Caldas</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2028,7 +2028,7 @@
         <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
@@ -2267,7 +2267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2284,7 +2284,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2292,12 +2292,12 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1025</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2305,12 +2305,12 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2331,12 +2331,12 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2349,37 +2349,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3. Pré-diagnóstico feito</t>
+          <t>1. Oportunidade</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. Oportunidade</t>
+          <t>5. Precificação/Aprovação em andamento</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5. Precificação/Aprovação em andamento</t>
+          <t>3. Pré-diagnóstico feito</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2388,7 +2388,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2396,7 +2396,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4. Diagnóstico feito</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/pipefy-crm/dados/relatorio_completo.xlsx
+++ b/pipefy-crm/dados/relatorio_completo.xlsx
@@ -465,16 +465,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>922</v>
+        <v>957</v>
       </c>
       <c r="D2" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="F2" t="n">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -487,22 +487,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G3" t="n">
-        <v>46.5</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="4">
@@ -518,16 +518,16 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -571,13 +571,13 @@
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="7">
@@ -593,10 +593,10 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>18</v>
@@ -633,11 +633,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sim, parcelamento</t>
+          <t>Sim, autoridade</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -646,38 +646,38 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>30.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sim, autoridade</t>
+          <t>Sim, parcelamento</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>8.300000000000001</v>
+        <v>30.8</v>
       </c>
     </row>
   </sheetData>
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -741,19 +741,19 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D2" t="n">
         <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="G2" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
@@ -766,13 +766,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
         <v>183</v>
@@ -791,19 +791,19 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="5">
@@ -859,51 +859,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Miguel Mendes Louzada de Souza</t>
+          <t>Jonas Pimenta</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jonas Pimenta</t>
+          <t>Miguel Mendes Louzada de Souza</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="9">
@@ -934,51 +934,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IGOR SILVA MONIZ</t>
+          <t>Manuella Heringer Rocha Verbicaro Ramos</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
         <v>97</v>
       </c>
       <c r="G10" t="n">
-        <v>7.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manuella Heringer Rocha Verbicaro Ramos</t>
+          <t>IGOR SILVA MONIZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="12">
@@ -991,10 +991,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1016,19 +1016,19 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G13" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1041,16 +1041,16 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
         <v>2.5</v>
@@ -1094,16 +1094,16 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17">
@@ -1116,13 +1116,13 @@
         <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>64</v>
@@ -1144,16 +1144,16 @@
         <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">
@@ -1163,22 +1163,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
         <v>33</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>30</v>
@@ -1222,13 +1222,13 @@
         <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="22">
@@ -1241,13 +1241,13 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
         <v>37</v>
@@ -1266,10 +1266,10 @@
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1291,10 +1291,10 @@
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1366,19 +1366,19 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G27" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="28">
@@ -1409,26 +1409,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Erik Branco Queiroz</t>
+          <t>brunacatalani1-20261</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1459,67 +1459,67 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gabriel Pereira</t>
+          <t>Erik Branco Queiroz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gabriela D’Agostini Fraga</t>
+          <t>Gabriel Pereira</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>6.7</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Davison Dhiego de Farias Mazzei</t>
+          <t>Gabriela D’Agostini Fraga</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1528,32 +1528,32 @@
         <v>15</v>
       </c>
       <c r="G33" t="n">
-        <v>13.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pedro de Souza Angelo</t>
+          <t>Davison Dhiego de Farias Mazzei</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G34" t="n">
-        <v>45.5</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="35">
@@ -1566,13 +1566,13 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>11</v>
@@ -1584,76 +1584,76 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Heitor Mendes</t>
+          <t>Pedro de Souza Angelo</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enzo Antunes Marmello</t>
+          <t>Heitor Mendes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
-        <v>44.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gilson Batista Machado Martins</t>
+          <t>Enzo Antunes Marmello</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G38" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
@@ -1684,39 +1684,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sem responsável</t>
+          <t>Gilson Batista Machado Martins</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>natalia-rodrigues-poli</t>
+          <t>wallisonpereira-20221-poli</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1728,101 +1728,101 @@
         <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>João Victor Moraes</t>
+          <t>natalia-rodrigues-poli</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>wallisonpereira-20221-poli</t>
+          <t>João Victor Moraes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Renato Saboia</t>
+          <t>Clara Guedes Fernandes</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Clara Guedes Fernandes</t>
+          <t>Eduarda Braun Monteiro da Silva</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -1834,20 +1834,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Eduarda Braun Monteiro da Silva</t>
+          <t>Sem responsável</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
@@ -1859,39 +1859,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>brunacatalani1-20261</t>
+          <t>Renato Saboia</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cecília Nogueira Rosa</t>
+          <t>Stella Monteiro</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -1922,38 +1922,38 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Stella Monteiro</t>
+          <t>Cecília Nogueira Rosa</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51">
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2034,17 +2034,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Arthur Catelani Gomes da Silva</t>
+          <t>Heitor Ferreira</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2053,23 +2053,23 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Heitor Ferreira</t>
+          <t>Guilherme Lameck</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Guilherme Lameck</t>
+          <t>Arthur Catelani Gomes da Silva</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">
@@ -2134,17 +2134,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LUCAS CORDEIRO QUIRINO</t>
+          <t>Rafael Gondim</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2153,20 +2153,20 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Rafael Gondim</t>
+          <t>ericheubel-20241</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2178,13 +2178,13 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ericheubel-20241</t>
+          <t>leonardorussosalles</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2209,7 +2209,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>leonardorussosalles</t>
+          <t>liviamonteiro-poli</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2228,31 +2228,6 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>liviamonteiro-poli</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2292,7 +2267,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1038</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="3">
@@ -2305,7 +2280,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
@@ -2318,7 +2293,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -2331,7 +2306,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -2344,55 +2319,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. Oportunidade</t>
+          <t>3. Pré-diagnóstico feito</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5. Precificação/Aprovação em andamento</t>
+          <t>1. Oportunidade</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3. Pré-diagnóstico feito</t>
+          <t>5. Precificação/Aprovação em andamento</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6. Proposta comercial feita</t>
+          <t>4. Diagnóstico feito</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2401,15 +2376,15 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4. Diagnóstico feito</t>
+          <t>6. Proposta comercial feita</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/pipefy-crm/dados/relatorio_completo.xlsx
+++ b/pipefy-crm/dados/relatorio_completo.xlsx
@@ -465,16 +465,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>957</v>
+        <v>966</v>
       </c>
       <c r="D2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>1106</v>
+        <v>1121</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -741,7 +741,7 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D2" t="n">
         <v>23</v>
@@ -750,7 +750,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G2" t="n">
         <v>7.5</v>
@@ -772,10 +772,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G3" t="n">
         <v>2.7</v>
@@ -859,101 +859,101 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jonas Pimenta</t>
+          <t>Miguel Mendes Louzada de Souza</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Miguel Mendes Louzada de Souza</t>
+          <t>Jonas Pimenta</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G8" t="n">
-        <v>5.9</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agatha Frossard</t>
+          <t>Manuella Heringer Rocha Verbicaro Ramos</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G9" t="n">
-        <v>10.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Manuella Heringer Rocha Verbicaro Ramos</t>
+          <t>Agatha Frossard</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="11">
@@ -1009,51 +1009,51 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rodrigo Polly Anthés</t>
+          <t>Camilla Ribeiro Ferreira</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>86</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Camilla Ribeiro Ferreira</t>
+          <t>Rodrigo Polly Anthés</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1241,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1250,10 +1250,10 @@
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -1372,13 +1372,13 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G27" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="28">
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
         <v>19</v>
@@ -1709,26 +1709,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>wallisonpereira-20221-poli</t>
+          <t>João Victor Moraes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
         <v>3</v>
       </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>40</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="42">
@@ -1759,26 +1759,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>João Victor Moraes</t>
+          <t>wallisonpereira-20221-poli</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -1834,64 +1834,64 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sem responsável</t>
+          <t>Renato Saboia</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Renato Saboia</t>
+          <t>Stella Monteiro</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stella Monteiro</t>
+          <t>Vitor Malfa</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -1903,32 +1903,32 @@
         <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Vitor Malfa</t>
+          <t>Lucas Angelo Ribeiro</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1959,17 +1959,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lucas Angelo Ribeiro</t>
+          <t>Mariana Fonseca</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -1984,17 +1984,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mariana Fonseca</t>
+          <t>Sem responsável</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1076</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="3">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -2332,46 +2332,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. Oportunidade</t>
+          <t>5. Precificação/Aprovação em andamento</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4. Diagnóstico feito</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>4</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>5. Precificação/Aprovação em andamento</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4. Diagnóstico feito</t>
+          <t>1. Oportunidade</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/pipefy-crm/dados/relatorio_completo.xlsx
+++ b/pipefy-crm/dados/relatorio_completo.xlsx
@@ -465,16 +465,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="D2" t="n">
         <v>108</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>1121</v>
+        <v>1140</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" t="n">
         <v>46</v>
@@ -496,13 +496,13 @@
         <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G3" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="4">
@@ -515,19 +515,19 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="5">
@@ -546,13 +546,13 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -593,10 +593,10 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>18</v>
@@ -640,13 +640,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>13</v>
@@ -668,10 +668,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>13</v>
@@ -741,16 +741,16 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D2" t="n">
         <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G2" t="n">
         <v>7.5</v>
@@ -766,13 +766,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
         <v>185</v>
@@ -866,19 +866,19 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="8">
@@ -894,10 +894,10 @@
         <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
         <v>122</v>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D9" t="n">
         <v>13</v>
@@ -925,10 +925,10 @@
         <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -984,51 +984,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gabriela Boechat</t>
+          <t>Camilla Ribeiro Ferreira</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G12" t="n">
-        <v>11.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Camilla Ribeiro Ferreira</t>
+          <t>Gabriela Boechat</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="14">
@@ -1241,13 +1241,13 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>38</v>
@@ -1366,19 +1366,19 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G27" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="28">
@@ -1419,10 +1419,10 @@
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
         <v>19</v>
@@ -1591,13 +1591,13 @@
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>11</v>
@@ -1791,13 +1791,13 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -1884,51 +1884,51 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Vitor Malfa</t>
+          <t>Sem responsável</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lucas Angelo Ribeiro</t>
+          <t>Vitor Malfa</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="50">
@@ -1959,17 +1959,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mariana Fonseca</t>
+          <t>Lucas Angelo Ribeiro</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -1984,17 +1984,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sem responsável</t>
+          <t>Mariana Fonseca</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1085</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="3">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -2306,16 +2306,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7. Follow-up</t>
+          <t>1. Oportunidade</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2324,28 +2324,28 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3. Pré-diagnóstico feito</t>
+          <t>7. Follow-up</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5. Precificação/Aprovação em andamento</t>
+          <t>3. Pré-diagnóstico feito</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -2358,16 +2358,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1. Oportunidade</t>
+          <t>6. Proposta comercial feita</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2376,11 +2376,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6. Proposta comercial feita</t>
+          <t>5. Precificação/Aprovação em andamento</t>
         </is>
       </c>
       <c r="C11" t="n">

--- a/pipefy-crm/dados/relatorio_completo.xlsx
+++ b/pipefy-crm/dados/relatorio_completo.xlsx
@@ -465,16 +465,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>976</v>
+        <v>997</v>
       </c>
       <c r="D2" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" t="n">
         <v>46</v>
@@ -496,13 +496,13 @@
         <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G3" t="n">
-        <v>45.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -546,13 +546,13 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6">
@@ -596,13 +596,13 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="8">
@@ -618,10 +618,10 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>15</v>
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -741,13 +741,13 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D2" t="n">
         <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
         <v>358</v>
@@ -766,16 +766,16 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G3" t="n">
         <v>2.7</v>
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -888,22 +888,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
         <v>122</v>
       </c>
       <c r="G8" t="n">
-        <v>10.7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="9">
@@ -916,19 +916,19 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" t="n">
         <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="10">
@@ -966,10 +966,10 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -991,16 +991,16 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G12" t="n">
         <v>2.2</v>
@@ -1091,19 +1091,19 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="17">
@@ -1209,101 +1209,101 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Guilherme Vanni de Lima Cavalcanti Wanderley</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Guilherme Vanni de Lima Cavalcanti Wanderley</t>
+          <t>Emmanuel</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Beatriz Assunção</t>
+          <t>Lucas Ninhaus</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pedro Carneiro Cavalcante</t>
+          <t>Beatriz Assunção</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>5.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1334,51 +1334,51 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gabriel Sanhudo Soares</t>
+          <t>Pedro Carneiro Cavalcante</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G26" t="n">
-        <v>28.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lucas Ninhaus</t>
+          <t>Gabriel Sanhudo Soares</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
-        <v>7.1</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="28">
@@ -1416,16 +1416,16 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
         <v>14</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1434,92 +1434,92 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Matheus Xavier Martins</t>
+          <t>Erik Branco Queiroz</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Erik Branco Queiroz</t>
+          <t>Gabriel Pereira</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
         <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>16.7</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gabriel Pereira</t>
+          <t>Matheus Xavier Martins</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>29.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gabriela D’Agostini Fraga</t>
+          <t>Davison Dhiego de Farias Mazzei</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1528,23 +1528,23 @@
         <v>15</v>
       </c>
       <c r="G33" t="n">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Davison Dhiego de Farias Mazzei</t>
+          <t>Gabriela D’Agostini Fraga</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="n">
-        <v>13.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="35">
@@ -1734,14 +1734,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>natalia-rodrigues-poli</t>
+          <t>wallisonpereira-20221-poli</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1753,51 +1753,51 @@
         <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>wallisonpereira-20221-poli</t>
+          <t>Clara Guedes Fernandes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
         <v>3</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Clara Guedes Fernandes</t>
+          <t>natalia-rodrigues-poli</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -1809,20 +1809,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Eduarda Braun Monteiro da Silva</t>
+          <t>Sem responsável</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -1834,17 +1834,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Renato Saboia</t>
+          <t>Eduarda Braun Monteiro da Silva</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1853,7 +1853,7 @@
         <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1884,67 +1884,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sem responsável</t>
+          <t>Vitor Malfa</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Vitor Malfa</t>
+          <t>Cecília Nogueira Rosa</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cecília Nogueira Rosa</t>
+          <t>Lucas Angelo Ribeiro</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -1953,23 +1953,23 @@
         <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lucas Angelo Ribeiro</t>
+          <t>Mariana Fonseca</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -1984,14 +1984,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mariana Fonseca</t>
+          <t>Eduardo Caldas</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2003,48 +2003,48 @@
         <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Eduardo Caldas</t>
+          <t>Heitor Ferreira</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Heitor Ferreira</t>
+          <t>Guilherme Lameck</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2059,14 +2059,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Guilherme Lameck</t>
+          <t>Arthur Catelani Gomes da Silva</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2078,13 +2078,13 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Arthur Catelani Gomes da Silva</t>
+          <t>Nicollas Viellas Lee</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2109,7 +2109,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nicollas Viellas Lee</t>
+          <t>Rafael Gondim</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2134,14 +2134,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rafael Gondim</t>
+          <t>ericheubel-20241</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2153,13 +2153,13 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ericheubel-20241</t>
+          <t>leonardorussosalles</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2184,7 +2184,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>leonardorussosalles</t>
+          <t>liviamonteiro-poli</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2203,31 +2203,6 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>liviamonteiro-poli</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2267,7 +2242,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1097</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="3">
@@ -2280,7 +2255,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">
@@ -2293,7 +2268,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
@@ -2311,80 +2286,80 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1. Oportunidade</t>
+          <t>7. Follow-up</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7. Follow-up</t>
+          <t>3. Pré-diagnóstico feito</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3. Pré-diagnóstico feito</t>
+          <t>4. Diagnóstico feito</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4. Diagnóstico feito</t>
+          <t>1. Oportunidade</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6. Proposta comercial feita</t>
+          <t>5. Precificação/Aprovação em andamento</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5. Precificação/Aprovação em andamento</t>
+          <t>6. Proposta comercial feita</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/pipefy-crm/dados/relatorio_completo.xlsx
+++ b/pipefy-crm/dados/relatorio_completo.xlsx
@@ -465,16 +465,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>997</v>
+        <v>1019</v>
       </c>
       <c r="D2" t="n">
         <v>110</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -493,16 +493,16 @@
         <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -515,19 +515,19 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="5">
@@ -571,13 +571,13 @@
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="7">
@@ -618,10 +618,10 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>15</v>
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,16 +866,16 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
@@ -894,16 +894,16 @@
         <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G8" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="9">
@@ -916,19 +916,19 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10">
@@ -966,10 +966,10 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -991,13 +991,13 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
         <v>9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>13</v>
       </c>
       <c r="F12" t="n">
         <v>93</v>
@@ -1016,10 +1016,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1222,13 +1222,13 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="22">
@@ -1266,13 +1266,13 @@
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F23" t="n">
         <v>39</v>
@@ -1322,13 +1322,13 @@
         <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="26">
@@ -1416,16 +1416,16 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" t="n">
         <v>3</v>
       </c>
-      <c r="D29" t="n">
-        <v>14</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4</v>
-      </c>
       <c r="F29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1434,51 +1434,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Erik Branco Queiroz</t>
+          <t>Gabriel Pereira</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G30" t="n">
-        <v>16.7</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gabriel Pereira</t>
+          <t>Erik Branco Queiroz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>27.8</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
@@ -1509,17 +1509,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Davison Dhiego de Farias Mazzei</t>
+          <t>Gabriela D’Agostini Fraga</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1528,23 +1528,23 @@
         <v>15</v>
       </c>
       <c r="G33" t="n">
-        <v>13.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gabriela D’Agostini Fraga</t>
+          <t>Davison Dhiego de Farias Mazzei</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="n">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="35">
@@ -1647,54 +1647,54 @@
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G38" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>marcos.paulo</t>
+          <t>João Victor Moraes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
         <v>7</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gilson Batista Machado Martins</t>
+          <t>marcos.paulo</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1703,32 +1703,32 @@
         <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>João Victor Moraes</t>
+          <t>Gilson Batista Machado Martins</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="42">
@@ -1759,20 +1759,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Clara Guedes Fernandes</t>
+          <t>natalia-rodrigues-poli</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>5</v>
@@ -1784,20 +1784,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>natalia-rodrigues-poli</t>
+          <t>Clara Guedes Fernandes</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -1809,20 +1809,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sem responsável</t>
+          <t>Eduarda Braun Monteiro da Silva</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -1834,7 +1834,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Eduarda Braun Monteiro da Silva</t>
+          <t>Sem responsável</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1859,14 +1859,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Stella Monteiro</t>
+          <t>Vitor Malfa</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -1878,20 +1878,20 @@
         <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Vitor Malfa</t>
+          <t>Stella Monteiro</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -1903,23 +1903,23 @@
         <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cecília Nogueira Rosa</t>
+          <t>Lucas Angelo Ribeiro</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -1928,23 +1928,23 @@
         <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lucas Angelo Ribeiro</t>
+          <t>Cecília Nogueira Rosa</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
         <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51">
@@ -2009,17 +2009,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Heitor Ferreira</t>
+          <t>Arthur Catelani Gomes da Silva</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -2028,23 +2028,23 @@
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Guilherme Lameck</t>
+          <t>Heitor Ferreira</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2059,14 +2059,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Arthur Catelani Gomes da Silva</t>
+          <t>Guilherme Lameck</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2078,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2109,11 +2109,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rafael Gondim</t>
+          <t>Luiza Pavani</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -2122,26 +2122,26 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ericheubel-20241</t>
+          <t>Rafael Gondim</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2153,13 +2153,13 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>leonardorussosalles</t>
+          <t>ericheubel-20241</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2184,25 +2184,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>leonardorussosalles</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>liviamonteiro-poli</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2217,7 +2242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2234,7 +2259,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2242,12 +2267,12 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1118</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2255,12 +2280,12 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2273,7 +2298,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2281,12 +2306,12 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2294,7 +2319,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -2303,11 +2328,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3. Pré-diagnóstico feito</t>
+          <t>4. Diagnóstico feito</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2316,50 +2341,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4. Diagnóstico feito</t>
+          <t>5. Precificação/Aprovação em andamento</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. Oportunidade</t>
+          <t>3. Pré-diagnóstico feito</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>5. Precificação/Aprovação em andamento</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>6. Proposta comercial feita</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/pipefy-crm/dados/relatorio_completo.xlsx
+++ b/pipefy-crm/dados/relatorio_completo.xlsx
@@ -465,16 +465,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1019</v>
+        <v>1036</v>
       </c>
       <c r="D2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>1156</v>
+        <v>1190</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -496,13 +496,13 @@
         <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G3" t="n">
-        <v>46</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="4">
@@ -615,13 +615,13 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>15</v>
@@ -766,13 +766,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
         <v>187</v>
@@ -866,144 +866,144 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jonas Pimenta</t>
+          <t>Manuella Heringer Rocha Verbicaro Ramos</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>91</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="n">
         <v>14</v>
       </c>
-      <c r="C8" t="n">
-        <v>80</v>
-      </c>
-      <c r="D8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7</v>
-      </c>
       <c r="F8" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G8" t="n">
-        <v>11.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manuella Heringer Rocha Verbicaro Ramos</t>
+          <t>Jonas Pimenta</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Agatha Frossard</t>
+          <t>Camilla Ribeiro Ferreira</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G10" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IGOR SILVA MONIZ</t>
+          <t>Agatha Frossard</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G11" t="n">
-        <v>7.3</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Camilla Ribeiro Ferreira</t>
+          <t>IGOR SILVA MONIZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="13">
@@ -1216,69 +1216,69 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Lucas Ninhaus</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
         <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lucas Ninhaus</t>
+          <t>Emmanuel</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="24">
@@ -1384,51 +1384,51 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Maria Vitória Gomes Martins</t>
+          <t>brunacatalani1-20261</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>brunacatalani1-20261</t>
+          <t>Maria Vitória Gomes Martins</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1522,13 +1522,13 @@
         <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="34">
@@ -1666,13 +1666,13 @@
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
         <v>7</v>
@@ -1791,13 +1791,13 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -1872,13 +1872,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
@@ -1922,10 +1922,10 @@
         <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1959,20 +1959,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mariana Fonseca</t>
+          <t>Luiza Pavani</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
         <v>2</v>
@@ -1984,14 +1984,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Eduardo Caldas</t>
+          <t>Mariana Fonseca</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2003,17 +2003,17 @@
         <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Arthur Catelani Gomes da Silva</t>
+          <t>Eduardo Caldas</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
         <v>100</v>
@@ -2084,7 +2084,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nicollas Viellas Lee</t>
+          <t>Arthur Catelani Gomes da Silva</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2109,11 +2109,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Luiza Pavani</t>
+          <t>Nicollas Viellas Lee</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1141</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="3">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -2324,15 +2324,15 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4. Diagnóstico feito</t>
+          <t>3. Pré-diagnóstico feito</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2345,20 +2345,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3. Pré-diagnóstico feito</t>
+          <t>4. Diagnóstico feito</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
